--- a/artfynd/A 4344-2026 artfynd.xlsx
+++ b/artfynd/A 4344-2026 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419939</v>
+        <v>123419941</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>605721</v>
+        <v>605662</v>
       </c>
       <c r="R2" t="n">
-        <v>6845753</v>
+        <v>6845770</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +749,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_3163</t>
+          <t>2024_3161</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:49</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:49</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,15 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419941</v>
+        <v>123419938</v>
       </c>
       <c r="B3" t="n">
-        <v>78455</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,31 +811,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>605662</v>
+        <v>605725</v>
       </c>
       <c r="R3" t="n">
-        <v>6845770</v>
+        <v>6845735</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +874,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_3161</t>
+          <t>2024_3164</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -899,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,19 +925,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123419942</v>
+        <v>123419939</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -974,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>605681</v>
+        <v>605721</v>
       </c>
       <c r="R4" t="n">
-        <v>6845739</v>
+        <v>6845753</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,7 +994,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_3160</t>
+          <t>2024_3163</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1014,7 +1004,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:05</t>
+          <t>07:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1024,12 +1014,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>födosök</t>
+          <t>07:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,7 +1034,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tove von Euler</t>
+          <t>Samuel Koont</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1060,47 +1045,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123419938</v>
+        <v>123419942</v>
       </c>
       <c r="B5" t="n">
-        <v>92328</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1109,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>605725</v>
+        <v>605681</v>
       </c>
       <c r="R5" t="n">
-        <v>6845735</v>
+        <v>6845739</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,7 +1114,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_3164</t>
+          <t>2024_3160</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1149,7 +1124,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1159,7 +1134,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>födosök</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1179,7 +1159,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Samuel Koont</t>
+          <t>Tove von Euler</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1193,16 +1173,11 @@
         <v>123419943</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1323,12 +1298,7 @@
         <v>123419940</v>
       </c>
       <c r="B7" t="n">
-        <v>5492</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5495</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
